--- a/output_ai/ai_preview_bom.xlsx
+++ b/output_ai/ai_preview_bom.xlsx
@@ -29,7 +29,7 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00F0B429"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -515,21 +515,21 @@
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIRAAL 3D GEAR ENGINE — GEAR BILL OF MATERIALS</t>
+          <t>SIRAAL 3D GEAR ENGINE — BILL OF MATERIALS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>IS 2535 / ISO 1328  |  Involute 20°  |  1st Angle  |  TN-IMPACT 2026  |  P1=Teeth Z (N_starts for Worm)  P2=Module m(mm)  P3=Face Width(mm)  P4=Bore Dia(mm) or Ring Thk</t>
+          <t>IS 2535 / ISO 1328  |  Involute 20°  |  TN-IMPACT 2026  |  1st Angle Projection</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>#</t>
@@ -552,26 +552,22 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Param_1
-(Z / Starts)</t>
+          <t>Param_1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Param_2
-(Module m)</t>
+          <t>Param_2</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Param_3
-(Face Width)</t>
+          <t>Param_3</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Param_4
-(Bore Dia)</t>
+          <t>Param_4</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -601,8 +597,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Est_Cost
-(Rs)</t>
+          <t>Est_Cost_Rs</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -622,12 +617,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>AI-PREV-BRACK</t>
+          <t>AI-PREV-RADIAL_COO</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Custom_brack</t>
+          <t>Custom_Radial_Cooling_Hub</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">

--- a/output_ai/ai_preview_bom.xlsx
+++ b/output_ai/ai_preview_bom.xlsx
@@ -617,12 +617,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>AI-PREV-RADIAL_COO</t>
+          <t>AI-PREV-BIO_LIGHTW</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Custom_Radial_Cooling_Hub</t>
+          <t>Custom_Bio_Lightweight_Bracket</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
